--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487613_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487613_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.404199999999999</v>
+        <v>7.6739</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0375</v>
+        <v>5.7978</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3667</v>
+        <v>1.8761</v>
       </c>
       <c r="G2" t="n">
         <v>6.3108</v>
@@ -610,13 +610,13 @@
         <v>1.5523</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5577</v>
+        <v>1.8273</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5298</v>
+        <v>1.2901</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0279</v>
+        <v>0.5373</v>
       </c>
       <c r="V2" t="n">
         <v>0.894</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.1054</v>
+        <v>6.1476</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5825</v>
+        <v>4.1426</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5229</v>
+        <v>2.0051</v>
       </c>
       <c r="G3" t="n">
         <v>4.2231</v>
@@ -688,13 +688,13 @@
         <v>0.7761</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9092</v>
+        <v>0.9514</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6079</v>
+        <v>0.1679</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3013</v>
+        <v>0.7835</v>
       </c>
       <c r="V3" t="n">
         <v>3.1075</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. HERMOSO ALCUBILLA</t>
+          <t>P. FUENTE DIEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9815</v>
+        <v>3.8135</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1904</v>
+        <v>2.842</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7911</v>
+        <v>0.9714</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4006</v>
+        <v>2.3866</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5042</v>
+        <v>0.5536</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9048</v>
+        <v>1.833</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0537</v>
+        <v>2.2877</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0958</v>
+        <v>0.9886</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1495</v>
+        <v>1.2991</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3469</v>
+        <v>0.0989</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5916</v>
+        <v>-0.435</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2447</v>
+        <v>0.5339</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5821</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5523</v>
+        <v>0.5821</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3896</v>
+        <v>0.309</v>
       </c>
       <c r="T4" t="n">
-        <v>2.8039</v>
+        <v>0.0185</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5857</v>
+        <v>0.2905</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4104</v>
+        <v>1.506</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4104</v>
+        <v>1.506</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. FUENTE DIEZ</t>
+          <t>E. PASCUAL COZAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3347</v>
+        <v>3.7358</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5813</v>
+        <v>2.5965</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7534</v>
+        <v>1.1393</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3866</v>
+        <v>2.6052</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5536</v>
+        <v>2.3266</v>
       </c>
       <c r="I5" t="n">
-        <v>1.833</v>
+        <v>0.2786</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2877</v>
+        <v>2.6015</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9886</v>
+        <v>2.5787</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2991</v>
+        <v>0.0228</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0989</v>
+        <v>0.0037</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.435</v>
+        <v>-0.2521</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5339</v>
+        <v>0.2558</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3881</v>
+        <v>0.7761</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1698</v>
+        <v>0.3544</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2423</v>
+        <v>-0.0051</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0725</v>
+        <v>0.3595</v>
       </c>
       <c r="V5" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GARCIA-LARRACHE SEGURA</t>
+          <t>M. HERMOSO ALCUBILLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1864</v>
+        <v>3.4955</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3347</v>
+        <v>1.9497</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8517</v>
+        <v>1.5458</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7119</v>
+        <v>-0.4006</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4739</v>
+        <v>0.5042</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1858</v>
+        <v>-0.9048</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7074</v>
+        <v>-0.0537</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1493</v>
+        <v>1.0958</v>
       </c>
       <c r="L6" t="n">
-        <v>3.8567</v>
+        <v>-1.1495</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0045</v>
+        <v>-0.3469</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3246</v>
+        <v>-0.5916</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3291</v>
+        <v>0.2447</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.7463</v>
+        <v>0.5821</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9388</v>
+        <v>1.9036</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2557</v>
+        <v>1.5632</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6831</v>
+        <v>0.3404</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2821</v>
+        <v>1.4104</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2821</v>
+        <v>1.4104</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. PASCUAL COZAR</t>
+          <t>J. GARCIA-LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7809</v>
+        <v>3.3715</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9959</v>
+        <v>0.656</v>
       </c>
       <c r="F7" t="n">
-        <v>0.785</v>
+        <v>2.7155</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6052</v>
+        <v>3.7119</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3266</v>
+        <v>-1.4739</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2786</v>
+        <v>5.1858</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6015</v>
+        <v>2.7074</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5787</v>
+        <v>-1.1493</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0228</v>
+        <v>3.8567</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0037</v>
+        <v>1.0045</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2521</v>
+        <v>-0.3246</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2558</v>
+        <v>1.3291</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7761</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6005</v>
+        <v>1.1238</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6057</v>
+        <v>0.577</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0052</v>
+        <v>0.5468</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. KREISLER LORENTE</t>
+          <t>L. GARCIA LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1586</v>
+        <v>2.8096</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9318</v>
+        <v>1.9073</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2268</v>
+        <v>0.9023</v>
       </c>
       <c r="G8" t="n">
-        <v>1.395</v>
+        <v>1.4895</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4663</v>
+        <v>1.2226</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8613</v>
+        <v>0.2669</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4029</v>
+        <v>1.5699</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1977</v>
+        <v>2.0926</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2052</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0804</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6641</v>
+        <v>-0.87</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6562</v>
+        <v>0.7897</v>
       </c>
       <c r="P8" t="n">
+        <v>0.5821</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.9403</v>
-      </c>
       <c r="R8" t="n">
-        <v>0.9702</v>
+        <v>1.5523</v>
       </c>
       <c r="S8" t="n">
-        <v>1.074</v>
+        <v>0.6424</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4692</v>
+        <v>0.6956</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3952</v>
+        <v>-0.0532</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6597</v>
+        <v>0.0955</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6597</v>
+        <v>-0.5164</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. GARCIA LARRACHE SEGURA</t>
+          <t>M. KREISLER LORENTE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.0032</v>
+        <v>1.9729</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3463</v>
+        <v>0.3918</v>
       </c>
       <c r="F9" t="n">
-        <v>0.657</v>
+        <v>1.5811</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4895</v>
+        <v>1.395</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2226</v>
+        <v>-0.4663</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2669</v>
+        <v>1.8613</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5699</v>
+        <v>1.4029</v>
       </c>
       <c r="K9" t="n">
-        <v>2.0926</v>
+        <v>0.1977</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5227000000000001</v>
+        <v>1.2052</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0804</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.87</v>
+        <v>-0.6641</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7897</v>
+        <v>0.6562</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5821</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5523</v>
+        <v>0.9702</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.164</v>
+        <v>0.8883</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1346</v>
+        <v>0.9292</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2985</v>
+        <v>-0.0409</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0955</v>
+        <v>0.6597</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5164</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. LASUNCION MARIBLANCA</t>
+          <t>E. MARTINEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9</v>
+        <v>-4.6427</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.963</v>
+        <v>-3.7307</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.937</v>
+        <v>-0.9121</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1671</v>
+        <v>-5.0956</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0611</v>
+        <v>-2.0498</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.106</v>
+        <v>-3.0458</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.1756</v>
+        <v>-3.675</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2142</v>
+        <v>-1.0463</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.9614</v>
+        <v>-2.6287</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9916</v>
+        <v>-1.4206</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8469</v>
+        <v>-1.0035</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1446</v>
+        <v>-0.4171</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.194</v>
+        <v>1.1642</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>0.297</v>
+        <v>0.2305</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1828</v>
+        <v>0.2742</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1142</v>
+        <v>-0.0437</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8358</v>
+        <v>-0.9418</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8358</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. MARTINEZ ALVAREZ</t>
+          <t>N. LASUNCION MARIBLANCA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.9163</v>
+        <v>-4.6665</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7317</v>
+        <v>-2.7022</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1846</v>
+        <v>-1.9643</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.0956</v>
+        <v>-3.1671</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0498</v>
+        <v>-1.0611</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.0458</v>
+        <v>-2.106</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.675</v>
+        <v>-2.1756</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0463</v>
+        <v>-0.2142</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.6287</v>
+        <v>-1.9614</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4206</v>
+        <v>-0.9916</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0035</v>
+        <v>-0.8469</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4171</v>
+        <v>-0.1446</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1642</v>
+        <v>-0.194</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0431</v>
+        <v>0.5305</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7268</v>
+        <v>0.4436</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3163</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9418</v>
+        <v>-1.8358</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3299</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6119</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0631</v>
+        <v>-6.0298</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.7572</v>
+        <v>-5.6966</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3059</v>
+        <v>-0.3332</v>
       </c>
       <c r="G12" t="n">
         <v>-4.0326</v>
@@ -1390,13 +1390,13 @@
         <v>0.7761</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3576</v>
+        <v>0.3909</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0595</v>
+        <v>0.0011</v>
       </c>
       <c r="U12" t="n">
-        <v>0.417</v>
+        <v>0.3898</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2239</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>17.07550000000001</v>
+        <v>17.6813</v>
       </c>
       <c r="E13" t="n">
-        <v>7.548499999999998</v>
+        <v>8.154200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>9.527100000000001</v>
+        <v>9.526999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>9.426199999999996</v>
+        <v>9.426199999999998</v>
       </c>
       <c r="H13" t="n">
         <v>3.336700000000001</v>
@@ -1447,7 +1447,7 @@
         <v>11.007</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8623000000000001</v>
+        <v>0.8623000000000005</v>
       </c>
       <c r="M13" t="n">
         <v>-2.4431</v>
@@ -1456,7 +1456,7 @@
         <v>-7.670399999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>5.2275</v>
+        <v>5.227500000000001</v>
       </c>
       <c r="P13" t="n">
         <v>-4.8509</v>
@@ -1468,10 +1468,10 @@
         <v>11.642</v>
       </c>
       <c r="S13" t="n">
-        <v>8.5465</v>
+        <v>9.152099999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>5.349600000000001</v>
+        <v>5.9553</v>
       </c>
       <c r="U13" t="n">
         <v>3.1969</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.535</v>
+        <v>1.2146</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0032</v>
+        <v>1.6038</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4682</v>
+        <v>-0.3892</v>
       </c>
       <c r="G14" t="n">
         <v>1.0621</v>
@@ -1546,13 +1546,13 @@
         <v>2.3284</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2734</v>
+        <v>-0.5939</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1384</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.135</v>
+        <v>-0.0561</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6119</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. CUESTA DE SANTOS</t>
+          <t>M. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3386</v>
+        <v>0.1294</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1839</v>
+        <v>2.7639</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1547</v>
+        <v>-2.6345</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.1425</v>
+        <v>1.0596</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5141</v>
+        <v>0.9145</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.6566</v>
+        <v>0.1451</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0406</v>
+        <v>1.0938</v>
       </c>
       <c r="K15" t="n">
-        <v>2.002</v>
+        <v>1.071</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.9614</v>
+        <v>0.0228</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1831</v>
+        <v>-0.0342</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4879</v>
+        <v>-0.1565</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6952</v>
+        <v>0.1223</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3284</v>
+        <v>0.7761</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3284</v>
+        <v>0.7761</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1527</v>
+        <v>-0.8123</v>
       </c>
       <c r="T15" t="n">
-        <v>0.803</v>
+        <v>-0.1657</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6503</v>
+        <v>-0.6466</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.894</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6597</v>
+        <v>1.8358</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6597</v>
+        <v>-2.7298</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0052</v>
+        <v>-0.1038</v>
       </c>
       <c r="E16" t="n">
         <v>-0.1405</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1457</v>
+        <v>0.0367</v>
       </c>
       <c r="G16" t="n">
         <v>0.1631</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1579</v>
+        <v>-0.2669</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1817</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0238</v>
+        <v>-0.0852</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. LOBATO ANDRADE</t>
+          <t>H. SANTANA DE LA ROSA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0509</v>
+        <v>-0.4852</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7836</v>
+        <v>-0.1759</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7327</v>
+        <v>-0.3093</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2742</v>
+        <v>0.1419</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.193</v>
+        <v>-1.9179</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.08119999999999999</v>
+        <v>2.0598</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7934</v>
+        <v>0.6223</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4779</v>
+        <v>-1.3264</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2712</v>
+        <v>1.9486</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4808</v>
+        <v>-0.4804</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6708</v>
+        <v>-0.5916</v>
       </c>
       <c r="O17" t="n">
-        <v>1.1901</v>
+        <v>0.1112</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5821</v>
+        <v>1.3582</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5523</v>
+        <v>1.3582</v>
       </c>
       <c r="S17" t="n">
-        <v>1.583</v>
+        <v>-1.9375</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6397</v>
+        <v>-0.7504</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0567</v>
+        <v>-1.1872</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9418</v>
+        <v>-0.0478</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6597</v>
+        <v>-0.0478</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SANCHEZ SANCHEZ</t>
+          <t>C. CUESTA DE SANTOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5073</v>
+        <v>-0.5016</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2634</v>
+        <v>-0.8171</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.7708</v>
+        <v>0.3154</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0596</v>
+        <v>-2.1425</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9145</v>
+        <v>0.5141</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1451</v>
+        <v>-2.6566</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0938</v>
+        <v>0.0406</v>
       </c>
       <c r="K18" t="n">
-        <v>1.071</v>
+        <v>2.002</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0228</v>
+        <v>-1.9614</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0342</v>
+        <v>-2.1831</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1565</v>
+        <v>-1.4879</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1223</v>
+        <v>-0.6952</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7761</v>
+        <v>2.3284</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7761</v>
+        <v>2.3284</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4491</v>
+        <v>-0.6875</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6662</v>
+        <v>-0.198</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7828000000000001</v>
+        <v>-0.4895</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.894</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8358</v>
+        <v>-0.6597</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.7298</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. SANTANA DE LA ROSA</t>
+          <t>E. BOADA MONTESDEOCA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9918</v>
+        <v>-0.9806</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5763</v>
+        <v>-1.8576</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4155</v>
+        <v>0.877</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1419</v>
+        <v>0.1351</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9179</v>
+        <v>-0.5322</v>
       </c>
       <c r="I19" t="n">
-        <v>2.0598</v>
+        <v>0.6673</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6223</v>
+        <v>0.0247</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3264</v>
+        <v>0.0247</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9486</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4804</v>
+        <v>0.1104</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5916</v>
+        <v>-0.5569</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1112</v>
+        <v>0.6673</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3582</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3582</v>
+        <v>0.7761</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.4441</v>
+        <v>0.0485</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1508</v>
+        <v>0.058</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.2934</v>
+        <v>-0.0095</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0478</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.0478</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. BOADA MONTESDEOCA</t>
+          <t>J. LOBATO ANDRADE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2536</v>
+        <v>-1.5063</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1579</v>
+        <v>-1.8847</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9042</v>
+        <v>0.3784</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1351</v>
+        <v>-1.2742</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5322</v>
+        <v>-1.193</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6673</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0247</v>
+        <v>-0.7934</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0247</v>
+        <v>0.4779</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.2712</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1104</v>
+        <v>-0.4808</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5569</v>
+        <v>-1.6708</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6673</v>
+        <v>1.1901</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7761</v>
+        <v>1.5523</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2245</v>
+        <v>0.1276</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2423</v>
+        <v>0.5386</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0177</v>
+        <v>-0.411</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.9418</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.098</v>
+        <v>-2.0707</v>
       </c>
       <c r="E21" t="n">
         <v>-0.8078</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2901</v>
+        <v>-1.2629</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5042</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3699</v>
+        <v>-0.3426</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1817</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1882</v>
+        <v>-0.1609</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2239</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
+          <t>A. GOMEZ SERRANO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4124</v>
+        <v>-2.6484</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9409</v>
+        <v>-1.8988</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4715</v>
+        <v>-0.7496</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8642</v>
+        <v>-3.1333</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9565</v>
+        <v>-1.52</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.8208</v>
+        <v>-1.6133</v>
       </c>
       <c r="J22" t="n">
-        <v>1.4694</v>
+        <v>-1.9187</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7229</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2535</v>
+        <v>-1.997</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.3337</v>
+        <v>-1.2146</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7664</v>
+        <v>-1.5983</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5673</v>
+        <v>0.3837</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3284</v>
+        <v>1.1642</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-1.0091</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5002</v>
+        <v>-0.2622</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5722</v>
+        <v>-0.7469</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.894</v>
+        <v>0.3299</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.894</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. GOMEZ SERRANO</t>
+          <t>P. DOMINGUEZ LORENZO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.021</v>
+        <v>-2.715</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9989</v>
+        <v>-1.8534</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0222</v>
+        <v>-0.8616</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.1333</v>
+        <v>-0.6327</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.52</v>
+        <v>0.2776</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6133</v>
+        <v>-0.9104</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.9187</v>
+        <v>1.3712</v>
       </c>
       <c r="K23" t="n">
-        <v>0.07829999999999999</v>
+        <v>1.3306</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.997</v>
+        <v>0.0406</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2146</v>
+        <v>-2.0039</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5983</v>
+        <v>-1.0529</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3837</v>
+        <v>-0.951</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1642</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R23" t="n">
         <v>1.1642</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3818</v>
+        <v>-0.0538</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3623</v>
+        <v>-0.3141</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0195</v>
+        <v>0.2602</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3299</v>
+        <v>-0.2821</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.0478</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. DOMINGUEZ LORENZO</t>
+          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1699</v>
+        <v>-3.1431</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2538</v>
+        <v>-1.6416</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9161</v>
+        <v>-1.5016</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6327</v>
+        <v>-0.8642</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2776</v>
+        <v>0.9565</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9104</v>
+        <v>-1.8208</v>
       </c>
       <c r="J24" t="n">
-        <v>1.3712</v>
+        <v>1.4694</v>
       </c>
       <c r="K24" t="n">
-        <v>1.3306</v>
+        <v>2.7229</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0406</v>
+        <v>-1.2535</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.0039</v>
+        <v>-2.3337</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0529</v>
+        <v>-1.7664</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.951</v>
+        <v>-0.5673</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.7463</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q24" t="n">
         <v>-2.9105</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1642</v>
+        <v>2.3284</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5088</v>
+        <v>-0.8028</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7145</v>
+        <v>-0.2005</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2057</v>
+        <v>-0.6022</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2821</v>
+        <v>-0.894</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2821</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.4495</v>
+        <v>-3.5975</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.3179</v>
+        <v>-2.8174</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1316</v>
+        <v>-0.7801</v>
       </c>
       <c r="G25" t="n">
         <v>-3.437</v>
@@ -2404,13 +2404,13 @@
         <v>2.7164</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.4006</v>
+        <v>-1.5486</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.5018</v>
+        <v>-1.0013</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8988</v>
+        <v>-0.5473</v>
       </c>
       <c r="V25" t="n">
         <v>0.6119</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-17.0756</v>
+        <v>-16.4082</v>
       </c>
       <c r="E26" t="n">
         <v>-9.527100000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.548699999999999</v>
+        <v>-6.8813</v>
       </c>
       <c r="G26" t="n">
         <v>-9.426299999999999</v>
@@ -2458,7 +2458,7 @@
         <v>2.4432</v>
       </c>
       <c r="K26" t="n">
-        <v>7.670499999999999</v>
+        <v>7.6705</v>
       </c>
       <c r="L26" t="n">
         <v>-5.227300000000001</v>
@@ -2470,10 +2470,10 @@
         <v>-11.0069</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.8622</v>
+        <v>-0.8622000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>4.850700000000002</v>
+        <v>4.8507</v>
       </c>
       <c r="Q26" t="n">
         <v>-11.642</v>
@@ -2482,16 +2482,16 @@
         <v>16.4927</v>
       </c>
       <c r="S26" t="n">
-        <v>-8.5464</v>
+        <v>-7.878900000000002</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.196800000000001</v>
+        <v>-3.1968</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.3497</v>
+        <v>-4.6822</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.9537</v>
+        <v>-3.953700000000001</v>
       </c>
       <c r="W26" t="n">
         <v>2.8686</v>
